--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="26">
   <si>
     <t/>
   </si>
   <si>
-    <t>20070110</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ MDU700</t>
+    <t>20142908</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 VNL 900</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,37 +28,52 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20090042</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ VAN700</t>
-  </si>
-  <si>
-    <t>20046081</t>
-  </si>
-  <si>
-    <t>G/D 3IN1 MCCINO 10'S</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20142910</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 MDU 900</t>
+  </si>
+  <si>
+    <t>20096682</t>
+  </si>
+  <si>
+    <t>IDM KACANG JUMBO 80</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20060370</t>
-  </si>
-  <si>
-    <t>G/DAY CHOCOCINO 10'S</t>
-  </si>
-  <si>
-    <t>20060371</t>
-  </si>
-  <si>
-    <t>G/DAY VNL.LATTE 10'S</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20142495</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN 1L</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20096781</t>
+  </si>
+  <si>
+    <t>SEDAAP MI KR.SPCY 87</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20125555</t>
+  </si>
+  <si>
+    <t>SEDAP MI KRN CH/BL86</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
   <si>
     <t>20049556</t>
@@ -67,76 +82,13 @@
     <t>SEDAAP MIE AYM KR 88</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20096781</t>
-  </si>
-  <si>
-    <t>SEDAAP MI KR.SPCY 87</t>
-  </si>
-  <si>
-    <t>20125555</t>
-  </si>
-  <si>
-    <t>SEDAP MI KRN CH/BL86</t>
+    <t>6</t>
   </si>
   <si>
     <t>20136385</t>
   </si>
   <si>
     <t>SEDAAP GRG CHF.DVN93</t>
-  </si>
-  <si>
-    <t>10000652</t>
-  </si>
-  <si>
-    <t>INDOMI AYAM BWNG 69G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20137102</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO KN 76G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>10000184</t>
-  </si>
-  <si>
-    <t>INDOMI AYAM SPECL68G</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>10000713</t>
-  </si>
-  <si>
-    <t>INDOMI KLD AYAM 75G</t>
-  </si>
-  <si>
-    <t>10002560</t>
-  </si>
-  <si>
-    <t>INDOMI SOTO MIE 70GR</t>
-  </si>
-  <si>
-    <t>20007834</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO SPCL 75</t>
-  </si>
-  <si>
-    <t>20137101</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO PD.D 76</t>
   </si>
 </sst>
 </file>
@@ -529,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -632,7 +584,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>11</v>
@@ -640,10 +592,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -652,18 +604,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -672,18 +624,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -692,18 +644,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -712,169 +664,9 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
   <si>
     <t/>
   </si>
   <si>
-    <t>10008819</t>
-  </si>
-  <si>
-    <t>BANGO KCAP MNS 700 G</t>
+    <t>10038932</t>
+  </si>
+  <si>
+    <t>K/A SPC MIX 10x23 G</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,49 +28,52 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>10005838</t>
-  </si>
-  <si>
-    <t>FILMA MYK GR RF 2 L</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10003974</t>
-  </si>
-  <si>
-    <t>TROPICAL MYK BTL 2 L</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10022534</t>
+  </si>
+  <si>
+    <t>ABC KCP MNS PCH685G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20127600</t>
-  </si>
-  <si>
-    <t>CPTADEN J C.MT 225 G</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20084481</t>
+  </si>
+  <si>
+    <t>P/MIE P.DWR SQDAYM75</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20116823</t>
-  </si>
-  <si>
-    <t>CPTADEN J FRH 225 G</t>
+    <t>20091304</t>
+  </si>
+  <si>
+    <t>P/MIE GRG P.GLD AY75</t>
   </si>
   <si>
     <t>5</t>
+  </si>
+  <si>
+    <t>20140188</t>
+  </si>
+  <si>
+    <t>POP MI KARI LAVA 79G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20140189</t>
+  </si>
+  <si>
+    <t>POP MI BASO GRNT 77G</t>
   </si>
 </sst>
 </file>
@@ -463,13 +466,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -569,15 +572,15 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -586,10 +589,30 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>16</v>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU6AMKT.xlsx
+++ b/E/DU6AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
   <si>
     <t/>
   </si>
   <si>
-    <t>10038932</t>
-  </si>
-  <si>
-    <t>K/A SPC MIX 10x23 G</t>
+    <t>10029536</t>
+  </si>
+  <si>
+    <t>MR.BREAD TAWAR</t>
   </si>
   <si>
     <t>DU6AMKT</t>
@@ -28,52 +28,67 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>10008882</t>
+  </si>
+  <si>
+    <t>K/API KOPI SPCL 150G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10022534</t>
-  </si>
-  <si>
-    <t>ABC KCP MNS PCH685G</t>
+    <t>20027166</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP220</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>10003801</t>
+  </si>
+  <si>
+    <t>INDOMI JB A.PG 127 G</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20084481</t>
-  </si>
-  <si>
-    <t>P/MIE P.DWR SQDAYM75</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20091304</t>
-  </si>
-  <si>
-    <t>P/MIE GRG P.GLD AY75</t>
+    <t>10003800</t>
+  </si>
+  <si>
+    <t>INDOMI GR S.JB 129 G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20140188</t>
-  </si>
-  <si>
-    <t>POP MI KARI LAVA 79G</t>
+    <t>20130807</t>
+  </si>
+  <si>
+    <t>INDOMI GR RDNG 120 G</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20140189</t>
-  </si>
-  <si>
-    <t>POP MI BASO GRNT 77G</t>
+    <t>20142599</t>
+  </si>
+  <si>
+    <t>INDOMI G C.IJO 120 G</t>
   </si>
 </sst>
 </file>
@@ -466,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -552,15 +567,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -569,18 +584,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -589,18 +604,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -609,10 +624,30 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
